--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517822</v>
+        <v>123517819</v>
       </c>
       <c r="B2" t="n">
-        <v>74876</v>
+        <v>91411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6471</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629753</v>
+        <v>629929</v>
       </c>
       <c r="R2" t="n">
-        <v>6616308</v>
+        <v>6616425</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517816</v>
+        <v>123517817</v>
       </c>
       <c r="B3" t="n">
-        <v>90986</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629907</v>
+        <v>629852</v>
       </c>
       <c r="R3" t="n">
-        <v>6616352</v>
+        <v>6616268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517817</v>
+        <v>123517816</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>90986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629852</v>
+        <v>629907</v>
       </c>
       <c r="R4" t="n">
-        <v>6616268</v>
+        <v>6616352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517819</v>
+        <v>123517832</v>
       </c>
       <c r="B5" t="n">
-        <v>91411</v>
+        <v>106041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629929</v>
+        <v>629762</v>
       </c>
       <c r="R5" t="n">
-        <v>6616425</v>
+        <v>6616311</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517832</v>
+        <v>123517822</v>
       </c>
       <c r="B7" t="n">
-        <v>106041</v>
+        <v>74876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>6471</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629762</v>
+        <v>629753</v>
       </c>
       <c r="R7" t="n">
-        <v>6616311</v>
+        <v>6616308</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517819</v>
+        <v>123517822</v>
       </c>
       <c r="B2" t="n">
-        <v>91411</v>
+        <v>74882</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6471</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629929</v>
+        <v>629753</v>
       </c>
       <c r="R2" t="n">
-        <v>6616425</v>
+        <v>6616308</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517817</v>
+        <v>123517821</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>79161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6431</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629852</v>
+        <v>629767</v>
       </c>
       <c r="R3" t="n">
-        <v>6616268</v>
+        <v>6616312</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,7 +882,7 @@
         <v>123517816</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517832</v>
+        <v>123517817</v>
       </c>
       <c r="B5" t="n">
-        <v>106041</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629762</v>
+        <v>629852</v>
       </c>
       <c r="R5" t="n">
-        <v>6616311</v>
+        <v>6616268</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517821</v>
+        <v>123517832</v>
       </c>
       <c r="B6" t="n">
-        <v>79155</v>
+        <v>106058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6431</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629767</v>
+        <v>629762</v>
       </c>
       <c r="R6" t="n">
-        <v>6616312</v>
+        <v>6616311</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517822</v>
+        <v>123517819</v>
       </c>
       <c r="B7" t="n">
-        <v>74876</v>
+        <v>91428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6471</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629753</v>
+        <v>629929</v>
       </c>
       <c r="R7" t="n">
-        <v>6616308</v>
+        <v>6616425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517822</v>
+        <v>123517821</v>
       </c>
       <c r="B2" t="n">
-        <v>74882</v>
+        <v>79166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6471</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629753</v>
+        <v>629767</v>
       </c>
       <c r="R2" t="n">
-        <v>6616308</v>
+        <v>6616312</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517821</v>
+        <v>123517819</v>
       </c>
       <c r="B3" t="n">
-        <v>79161</v>
+        <v>91433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629767</v>
+        <v>629929</v>
       </c>
       <c r="R3" t="n">
-        <v>6616312</v>
+        <v>6616425</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517816</v>
+        <v>123517822</v>
       </c>
       <c r="B4" t="n">
-        <v>91003</v>
+        <v>74885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6471</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629907</v>
+        <v>629753</v>
       </c>
       <c r="R4" t="n">
-        <v>6616352</v>
+        <v>6616308</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517817</v>
+        <v>123517816</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629852</v>
+        <v>629907</v>
       </c>
       <c r="R5" t="n">
-        <v>6616268</v>
+        <v>6616352</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517832</v>
+        <v>123517817</v>
       </c>
       <c r="B6" t="n">
-        <v>106058</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629762</v>
+        <v>629852</v>
       </c>
       <c r="R6" t="n">
-        <v>6616311</v>
+        <v>6616268</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517819</v>
+        <v>123517832</v>
       </c>
       <c r="B7" t="n">
-        <v>91428</v>
+        <v>106076</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629929</v>
+        <v>629762</v>
       </c>
       <c r="R7" t="n">
-        <v>6616425</v>
+        <v>6616311</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123517821</v>
       </c>
       <c r="B2" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517819</v>
+        <v>123517816</v>
       </c>
       <c r="B3" t="n">
-        <v>91433</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629929</v>
+        <v>629907</v>
       </c>
       <c r="R3" t="n">
-        <v>6616425</v>
+        <v>6616352</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517822</v>
+        <v>123517832</v>
       </c>
       <c r="B4" t="n">
-        <v>74885</v>
+        <v>106078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6471</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629753</v>
+        <v>629762</v>
       </c>
       <c r="R4" t="n">
-        <v>6616308</v>
+        <v>6616311</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517816</v>
+        <v>123517822</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>74886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6471</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629907</v>
+        <v>629753</v>
       </c>
       <c r="R5" t="n">
-        <v>6616352</v>
+        <v>6616308</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
         <v>123517817</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517832</v>
+        <v>123517819</v>
       </c>
       <c r="B7" t="n">
-        <v>106076</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629762</v>
+        <v>629929</v>
       </c>
       <c r="R7" t="n">
-        <v>6616311</v>
+        <v>6616425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517816</v>
+        <v>123517832</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>106078</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629907</v>
+        <v>629762</v>
       </c>
       <c r="R3" t="n">
-        <v>6616352</v>
+        <v>6616311</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517832</v>
+        <v>123517816</v>
       </c>
       <c r="B4" t="n">
-        <v>106078</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629762</v>
+        <v>629907</v>
       </c>
       <c r="R4" t="n">
-        <v>6616311</v>
+        <v>6616352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517821</v>
+        <v>123517817</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629767</v>
+        <v>629852</v>
       </c>
       <c r="R2" t="n">
-        <v>6616312</v>
+        <v>6616268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +780,7 @@
         <v>123517832</v>
       </c>
       <c r="B3" t="n">
-        <v>106078</v>
+        <v>105653</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517816</v>
+        <v>123517821</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>79168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6431</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629907</v>
+        <v>629767</v>
       </c>
       <c r="R4" t="n">
-        <v>6616352</v>
+        <v>6616312</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517822</v>
+        <v>123517816</v>
       </c>
       <c r="B5" t="n">
-        <v>74886</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6471</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629753</v>
+        <v>629907</v>
       </c>
       <c r="R5" t="n">
-        <v>6616308</v>
+        <v>6616352</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517817</v>
+        <v>123517819</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>91435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629852</v>
+        <v>629929</v>
       </c>
       <c r="R6" t="n">
-        <v>6616268</v>
+        <v>6616425</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517819</v>
+        <v>123517822</v>
       </c>
       <c r="B7" t="n">
-        <v>91435</v>
+        <v>74886</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6471</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629929</v>
+        <v>629753</v>
       </c>
       <c r="R7" t="n">
-        <v>6616425</v>
+        <v>6616308</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517817</v>
+        <v>123517821</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>79168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629852</v>
+        <v>629767</v>
       </c>
       <c r="R2" t="n">
-        <v>6616268</v>
+        <v>6616312</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517832</v>
+        <v>123517816</v>
       </c>
       <c r="B3" t="n">
-        <v>105653</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629762</v>
+        <v>629907</v>
       </c>
       <c r="R3" t="n">
-        <v>6616311</v>
+        <v>6616352</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517821</v>
+        <v>123517819</v>
       </c>
       <c r="B4" t="n">
-        <v>79168</v>
+        <v>91435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6431</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629767</v>
+        <v>629929</v>
       </c>
       <c r="R4" t="n">
-        <v>6616312</v>
+        <v>6616425</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517816</v>
+        <v>123517832</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>105653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629907</v>
+        <v>629762</v>
       </c>
       <c r="R5" t="n">
-        <v>6616352</v>
+        <v>6616311</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517819</v>
+        <v>123517822</v>
       </c>
       <c r="B6" t="n">
-        <v>91435</v>
+        <v>74886</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6471</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629929</v>
+        <v>629753</v>
       </c>
       <c r="R6" t="n">
-        <v>6616425</v>
+        <v>6616308</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517822</v>
+        <v>123517817</v>
       </c>
       <c r="B7" t="n">
-        <v>74886</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6471</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629753</v>
+        <v>629852</v>
       </c>
       <c r="R7" t="n">
-        <v>6616308</v>
+        <v>6616268</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517821</v>
+        <v>123517819</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>91435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629767</v>
+        <v>629929</v>
       </c>
       <c r="R2" t="n">
-        <v>6616312</v>
+        <v>6616425</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517816</v>
+        <v>123517817</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629907</v>
+        <v>629852</v>
       </c>
       <c r="R3" t="n">
-        <v>6616352</v>
+        <v>6616268</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517819</v>
+        <v>123517821</v>
       </c>
       <c r="B4" t="n">
-        <v>91435</v>
+        <v>79168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6431</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629929</v>
+        <v>629767</v>
       </c>
       <c r="R4" t="n">
-        <v>6616425</v>
+        <v>6616312</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517817</v>
+        <v>123517816</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629852</v>
+        <v>629907</v>
       </c>
       <c r="R7" t="n">
-        <v>6616268</v>
+        <v>6616352</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517819</v>
+        <v>123517817</v>
       </c>
       <c r="B2" t="n">
-        <v>91435</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629929</v>
+        <v>629852</v>
       </c>
       <c r="R2" t="n">
-        <v>6616425</v>
+        <v>6616268</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517817</v>
+        <v>123517832</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>105654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629852</v>
+        <v>629762</v>
       </c>
       <c r="R3" t="n">
-        <v>6616268</v>
+        <v>6616311</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517832</v>
+        <v>123517822</v>
       </c>
       <c r="B5" t="n">
-        <v>105653</v>
+        <v>74886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>6471</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629762</v>
+        <v>629753</v>
       </c>
       <c r="R5" t="n">
-        <v>6616311</v>
+        <v>6616308</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517822</v>
+        <v>123517816</v>
       </c>
       <c r="B6" t="n">
-        <v>74886</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6471</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629753</v>
+        <v>629907</v>
       </c>
       <c r="R6" t="n">
-        <v>6616308</v>
+        <v>6616352</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517816</v>
+        <v>123517819</v>
       </c>
       <c r="B7" t="n">
-        <v>91010</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629907</v>
+        <v>629929</v>
       </c>
       <c r="R7" t="n">
-        <v>6616352</v>
+        <v>6616425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18037-2021 artfynd.xlsx
+++ b/artfynd/A 18037-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517832</v>
+        <v>123517821</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>79168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>6431</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629762</v>
+        <v>629767</v>
       </c>
       <c r="R3" t="n">
-        <v>6616311</v>
+        <v>6616312</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517821</v>
+        <v>123517819</v>
       </c>
       <c r="B4" t="n">
-        <v>79168</v>
+        <v>91435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6431</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629767</v>
+        <v>629929</v>
       </c>
       <c r="R4" t="n">
-        <v>6616312</v>
+        <v>6616425</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517822</v>
+        <v>123517816</v>
       </c>
       <c r="B5" t="n">
-        <v>74886</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6471</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629753</v>
+        <v>629907</v>
       </c>
       <c r="R5" t="n">
-        <v>6616308</v>
+        <v>6616352</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123517816</v>
+        <v>123517822</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>74886</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6471</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629907</v>
+        <v>629753</v>
       </c>
       <c r="R6" t="n">
-        <v>6616352</v>
+        <v>6616308</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123517819</v>
+        <v>123517832</v>
       </c>
       <c r="B7" t="n">
-        <v>91435</v>
+        <v>105654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629929</v>
+        <v>629762</v>
       </c>
       <c r="R7" t="n">
-        <v>6616425</v>
+        <v>6616311</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
